--- a/bling_teste.xlsx
+++ b/bling_teste.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="227">
   <si>
     <t>ID</t>
   </si>
@@ -193,6 +193,243 @@
     <t>Informações Adicionais</t>
   </si>
   <si>
+    <t>PAI-G01067</t>
+  </si>
+  <si>
+    <t>186124</t>
+  </si>
+  <si>
+    <t>PAI-G00301</t>
+  </si>
+  <si>
+    <t>170124</t>
+  </si>
+  <si>
+    <t>PAI-G01836</t>
+  </si>
+  <si>
+    <t>188335</t>
+  </si>
+  <si>
+    <t>188334</t>
+  </si>
+  <si>
+    <t>188333</t>
+  </si>
+  <si>
+    <t>PAI-G00060</t>
+  </si>
+  <si>
+    <t>188326</t>
+  </si>
+  <si>
+    <t>PAI-G00800</t>
+  </si>
+  <si>
+    <t>156168</t>
+  </si>
+  <si>
+    <t>156171</t>
+  </si>
+  <si>
+    <t>PAI-G00427</t>
+  </si>
+  <si>
+    <t>145160</t>
+  </si>
+  <si>
+    <t>PAI-G02327</t>
+  </si>
+  <si>
+    <t>7701</t>
+  </si>
+  <si>
+    <t>PAI-G01772</t>
+  </si>
+  <si>
+    <t>5948</t>
+  </si>
+  <si>
+    <t>5944</t>
+  </si>
+  <si>
+    <t>PAI-G00757</t>
+  </si>
+  <si>
+    <t>2302</t>
+  </si>
+  <si>
+    <t>PAI-G00637</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>PAI-G00380</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>PAI-G02094</t>
+  </si>
+  <si>
+    <t>6974</t>
+  </si>
+  <si>
+    <t>PAI-G01675</t>
+  </si>
+  <si>
+    <t>5699</t>
+  </si>
+  <si>
+    <t>PAI-G01207</t>
+  </si>
+  <si>
+    <t>3735</t>
+  </si>
+  <si>
+    <t>3738</t>
+  </si>
+  <si>
+    <t>PAI-G01216</t>
+  </si>
+  <si>
+    <t>3835</t>
+  </si>
+  <si>
+    <t>FITA DUREX 3M</t>
+  </si>
+  <si>
+    <t>Cor:TRANSPARENTE;Medida:12X50</t>
+  </si>
+  <si>
+    <t>BROCA VIDEA SDS PLUS IRWIN</t>
+  </si>
+  <si>
+    <t>Medida:10,0X160</t>
+  </si>
+  <si>
+    <t>RATOEIRA GAIOLA COM MOLA CHACONFER</t>
+  </si>
+  <si>
+    <t>Tamanho:PEQUENA</t>
+  </si>
+  <si>
+    <t>Tamanho:MEDIA</t>
+  </si>
+  <si>
+    <t>Tamanho:GRANDE</t>
+  </si>
+  <si>
+    <t>AGULHA GRANDE P/ FOGAO CHACONFER</t>
+  </si>
+  <si>
+    <t>DISCO FLAP CONICO STARRETT</t>
+  </si>
+  <si>
+    <t>Medida:115X040</t>
+  </si>
+  <si>
+    <t>Medida:115X080</t>
+  </si>
+  <si>
+    <t>CANETA ESFEROG CRISTAL BIC</t>
+  </si>
+  <si>
+    <t>Tamanho:MEDIA;Cor:AZUL</t>
+  </si>
+  <si>
+    <t>TUBO ESGOTO KRONA</t>
+  </si>
+  <si>
+    <t>Medida:100MM</t>
+  </si>
+  <si>
+    <t>PORTA SANFONADA MULTILIT PLASFLEX</t>
+  </si>
+  <si>
+    <t>Medida:84X210;Cor:BEGE</t>
+  </si>
+  <si>
+    <t>Medida:72X210;Cor:BRANCA</t>
+  </si>
+  <si>
+    <t>DESEMPENADEIRA INJEREST</t>
+  </si>
+  <si>
+    <t>Medida:18X30;Acabamento:LISA</t>
+  </si>
+  <si>
+    <t>CONDUITE B HIDROLETE</t>
+  </si>
+  <si>
+    <t>Medida:3/4;Capacidade:50M</t>
+  </si>
+  <si>
+    <t>CAIXA D'AGUA FORTLEV</t>
+  </si>
+  <si>
+    <t>Capacidade:500L;Outra Variação:COM TAMPA SP</t>
+  </si>
+  <si>
+    <t>SUPORTE PRATELEIRA LEVE OVER OVERTIME</t>
+  </si>
+  <si>
+    <t>Tamanho:20CM;Cor:BRANCO</t>
+  </si>
+  <si>
+    <t>PIA SINTETICA PP RORATO</t>
+  </si>
+  <si>
+    <t>Medida:1,20;Cor:PRETO</t>
+  </si>
+  <si>
+    <t>JOELHO ESGOTO KRONA</t>
+  </si>
+  <si>
+    <t>Medida:040X45</t>
+  </si>
+  <si>
+    <t>Medida:040X90</t>
+  </si>
+  <si>
+    <t>JOELHO SOLDAVEL KRONA</t>
+  </si>
+  <si>
+    <t>Medida:1 1/2X45</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>UN</t>
+  </si>
+  <si>
+    <t>CX</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Ativo</t>
+  </si>
+  <si>
+    <t>CONSTRUJA DISTR. DE MATERIAIS P/ CONSTRU</t>
+  </si>
+  <si>
+    <t>M.S.B. COMERCIO DE MATERIAIS PARA CONSTRUCAO</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>00000078930469</t>
   </si>
   <si>
@@ -251,81 +488,6 @@
   </si>
   <si>
     <t>01234567018850</t>
-  </si>
-  <si>
-    <t>Cor:TRANSPARENTE;Medida:12X50</t>
-  </si>
-  <si>
-    <t>Medida:10,0X160</t>
-  </si>
-  <si>
-    <t>Tamanho:PEQUENA</t>
-  </si>
-  <si>
-    <t>Tamanho:MEDIA</t>
-  </si>
-  <si>
-    <t>Tamanho:GRANDE</t>
-  </si>
-  <si>
-    <t>Medida:115X040</t>
-  </si>
-  <si>
-    <t>Medida:115X080</t>
-  </si>
-  <si>
-    <t>Tamanho:MEDIA;Cor:AZUL</t>
-  </si>
-  <si>
-    <t>Medida:100MM</t>
-  </si>
-  <si>
-    <t>Medida:84X210;Cor:BEGE</t>
-  </si>
-  <si>
-    <t>Medida:72X210;Cor:BRANCA</t>
-  </si>
-  <si>
-    <t>Medida:18X30;Acabamento:LISA</t>
-  </si>
-  <si>
-    <t>Medida:3/4;Capacidade:50M</t>
-  </si>
-  <si>
-    <t>Capacidade:500L;Outra Variação:COM TAMPA SP</t>
-  </si>
-  <si>
-    <t>Tamanho:20CM;Cor:BRANCO</t>
-  </si>
-  <si>
-    <t>Medida:1,20;Cor:PRETO</t>
-  </si>
-  <si>
-    <t>Medida:040X45</t>
-  </si>
-  <si>
-    <t>Medida:040X90</t>
-  </si>
-  <si>
-    <t>Medida:1 1/2X45</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Ativo</t>
-  </si>
-  <si>
-    <t>CONSTRUJA DISTR. DE MATERIAIS P/ CONSTRU</t>
-  </si>
-  <si>
-    <t>M.S.B. COMERCIO DE MATERIAIS PARA CONSTRUCAO</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
   <si>
     <t>A Fita Durex 3M transparente é uma fita adesiva versátil e prática para uso diário. Com boa transparência e resistência, é indicada para diversas aplicações em escritórios, escolas e residências.
@@ -455,6 +617,51 @@
 Este produto possui variações disponíveis conforme especificações técnicas.</t>
   </si>
   <si>
+    <t>G01067</t>
+  </si>
+  <si>
+    <t>G00301</t>
+  </si>
+  <si>
+    <t>G01836</t>
+  </si>
+  <si>
+    <t>G00060</t>
+  </si>
+  <si>
+    <t>G00800</t>
+  </si>
+  <si>
+    <t>G00427</t>
+  </si>
+  <si>
+    <t>G02327</t>
+  </si>
+  <si>
+    <t>G01772</t>
+  </si>
+  <si>
+    <t>G00757</t>
+  </si>
+  <si>
+    <t>G00637</t>
+  </si>
+  <si>
+    <t>G00380</t>
+  </si>
+  <si>
+    <t>G02094</t>
+  </si>
+  <si>
+    <t>G01675</t>
+  </si>
+  <si>
+    <t>G01207</t>
+  </si>
+  <si>
+    <t>G01216</t>
+  </si>
+  <si>
     <t>3M</t>
   </si>
   <si>
@@ -489,66 +696,6 @@
   </si>
   <si>
     <t>RORATO</t>
-  </si>
-  <si>
-    <t>FITA DUREX TRANSP 12X50 3M</t>
-  </si>
-  <si>
-    <t>BROCA VIDEA SDS PLUS 10,0X160 IRWIN</t>
-  </si>
-  <si>
-    <t>RATOEIRA GAIOLA C/MOLA PEQUENA* CHACONFER</t>
-  </si>
-  <si>
-    <t>RATOEIRA GAIOLA C/MOLA MEDIA CHACONFER</t>
-  </si>
-  <si>
-    <t>RATOEIRA GAIOLA C/MOLA GRANDE CHACONFER</t>
-  </si>
-  <si>
-    <t>AGULHA GRANDE P/ FOGAO C/50 CHACONFER</t>
-  </si>
-  <si>
-    <t>DISCO FLAP CONICO 115X040 STARRETT</t>
-  </si>
-  <si>
-    <t>DISCO FLAP CONICO 115X080 STARRETT</t>
-  </si>
-  <si>
-    <t>CANETA ESFEROG MEDIA 1.0 AZ CRISTAL* BIC</t>
-  </si>
-  <si>
-    <t>TUBO ESG. PRIM. 100MM KRONA</t>
-  </si>
-  <si>
-    <t>PORTA SANF 84X210 BEGE - MULTILIT PLASFLEX</t>
-  </si>
-  <si>
-    <t>PORTA SANF 72X210 BRANCA - MULTILIT PLASFLEX</t>
-  </si>
-  <si>
-    <t>DESEMP. AZ LISA 18X30 C/06 - INJEREST</t>
-  </si>
-  <si>
-    <t>CONDUITE (B) 3/4" AM 50M - HIDROLET HIDROLETE</t>
-  </si>
-  <si>
-    <t>CAIXA DAGUA 500L C/TAMPA - FORTLEV FORTLEV SP</t>
-  </si>
-  <si>
-    <t>SUPORTE PRAT. LEVE 20CM BR C/12 -OVER OVERTIME</t>
-  </si>
-  <si>
-    <t>PIA SINTETICA 1.20 PRETO (PP) - RORATO</t>
-  </si>
-  <si>
-    <t>JOELHO ESG. 040X45 C/25 KRONA</t>
-  </si>
-  <si>
-    <t>JOELHO ESG. 040X90 C/50 KRONA</t>
-  </si>
-  <si>
-    <t>JOELHO SOLD. 11/2X45 C/10 KRONA</t>
   </si>
   <si>
     <t>https://pub-6b1902641e5a40b2916ddf51bb1dfedf.r2.dev/1_FITA_DUREX_TRANSP_12X50_3M.jpg|https://pub-6b1902641e5a40b2916ddf51bb1dfedf.r2.dev/2_FITA_DUREX_TRANSP_12X50_3M.jpg|https://pub-6b1902641e5a40b2916ddf51bb1dfedf.r2.dev/3_FITA_DUREX_TRANSP_12X50_3M.jpg|https://cdn.construja.com.br/produtos/186124/186124.jpg</t>
@@ -1000,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BG21"/>
+  <dimension ref="A1:BG36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:59">
@@ -1187,34 +1334,37 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>94</v>
+      </c>
+      <c r="D2" t="s">
+        <v>128</v>
       </c>
       <c r="E2">
         <v>39191010</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G2">
         <v>9.869999999999999</v>
       </c>
       <c r="J2" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K2" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L2">
         <v>3.544</v>
       </c>
       <c r="N2" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="P2" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q2" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R2">
         <v>0.032</v>
@@ -1232,28 +1382,28 @@
         <v>10</v>
       </c>
       <c r="Z2" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="AA2" t="s">
-        <v>104</v>
+        <v>158</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>173</v>
       </c>
       <c r="AM2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="AV2" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="AZ2" t="s">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="BF2" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:59">
@@ -1261,73 +1411,85 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
+        <v>128</v>
       </c>
       <c r="E3">
-        <v>82075011</v>
+        <v>39191010</v>
       </c>
       <c r="F3" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G3">
-        <v>23.26</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="J3" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K3" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L3">
-        <v>13.282</v>
+        <v>3.544</v>
       </c>
       <c r="N3" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="P3" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q3" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R3">
-        <v>0.07000000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="S3">
-        <v>0.07000000000000001</v>
+        <v>0.032</v>
+      </c>
+      <c r="T3" t="s">
+        <v>138</v>
+      </c>
+      <c r="U3" t="s">
+        <v>138</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="W3">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="X3">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="Z3" t="s">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="AA3" t="s">
-        <v>105</v>
+        <v>158</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>173</v>
       </c>
       <c r="AM3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="AR3" s="2" t="s">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="AV3" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="AZ3" t="s">
-        <v>173</v>
+        <v>221</v>
       </c>
       <c r="BF3" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:59">
@@ -1335,73 +1497,76 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>96</v>
+      </c>
+      <c r="D4" t="s">
+        <v>128</v>
       </c>
       <c r="E4">
-        <v>73262000</v>
+        <v>82075011</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G4">
-        <v>31.28</v>
+        <v>23.26</v>
       </c>
       <c r="J4" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K4" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L4">
-        <v>19.115</v>
+        <v>13.282</v>
       </c>
       <c r="N4" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="P4" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q4" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R4">
-        <v>0.768</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S4">
-        <v>0.768</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V4">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="X4">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="Z4" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="AA4" t="s">
-        <v>106</v>
+        <v>159</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>174</v>
       </c>
       <c r="AM4" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>133</v>
+        <v>189</v>
       </c>
       <c r="AR4" s="2" t="s">
-        <v>153</v>
+        <v>201</v>
       </c>
       <c r="AV4" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="AZ4" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="BF4" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:59">
@@ -1409,73 +1574,85 @@
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>97</v>
+      </c>
+      <c r="D5" t="s">
+        <v>128</v>
       </c>
       <c r="E5">
-        <v>73262000</v>
+        <v>82075011</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G5">
-        <v>37.93</v>
+        <v>23.26</v>
       </c>
       <c r="J5" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K5" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L5">
-        <v>23.95</v>
+        <v>13.282</v>
       </c>
       <c r="N5" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="P5" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q5" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R5">
-        <v>0.632</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S5">
-        <v>0.632</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T5" t="s">
+        <v>139</v>
+      </c>
+      <c r="U5" t="s">
+        <v>139</v>
       </c>
       <c r="V5">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="X5">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="AA5" t="s">
-        <v>106</v>
+        <v>159</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>174</v>
       </c>
       <c r="AM5" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="AR5" s="2" t="s">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="AV5" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="AZ5" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="BF5" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:59">
@@ -1483,144 +1660,162 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>98</v>
+      </c>
+      <c r="D6" t="s">
+        <v>128</v>
       </c>
       <c r="E6">
         <v>73262000</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G6">
-        <v>44.86</v>
+        <v>31.28</v>
       </c>
       <c r="J6" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K6" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L6">
-        <v>28.99</v>
+        <v>19.115</v>
       </c>
       <c r="N6" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="P6" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q6" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R6">
-        <v>0.6850000000000001</v>
+        <v>0.768</v>
       </c>
       <c r="S6">
-        <v>0.6850000000000001</v>
+        <v>0.768</v>
       </c>
       <c r="V6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W6">
+        <v>12</v>
+      </c>
+      <c r="X6">
         <v>15</v>
       </c>
-      <c r="X6">
-        <v>16</v>
-      </c>
       <c r="Z6" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="AA6" t="s">
-        <v>106</v>
+        <v>160</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>175</v>
       </c>
       <c r="AM6" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="AR6" s="2" t="s">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="AV6" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="AZ6" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="BF6" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:59">
       <c r="B7" t="s">
         <v>64</v>
       </c>
+      <c r="C7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" t="s">
+        <v>128</v>
+      </c>
       <c r="E7">
-        <v>73199000</v>
+        <v>73262000</v>
       </c>
       <c r="F7" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G7">
-        <v>14.69</v>
+        <v>31.28</v>
       </c>
       <c r="J7" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K7" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L7">
-        <v>7.049</v>
+        <v>19.115</v>
       </c>
       <c r="N7" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="P7" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q7" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R7">
-        <v>0.076</v>
+        <v>0.768</v>
       </c>
       <c r="S7">
-        <v>0.076</v>
+        <v>0.768</v>
+      </c>
+      <c r="T7" t="s">
+        <v>140</v>
+      </c>
+      <c r="U7" t="s">
+        <v>140</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="AA7" t="s">
-        <v>107</v>
+        <v>160</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>175</v>
       </c>
       <c r="AM7" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>136</v>
+        <v>190</v>
       </c>
       <c r="AR7" s="2" t="s">
-        <v>156</v>
+        <v>202</v>
       </c>
       <c r="AV7" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="AZ7" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="BF7" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:59">
@@ -1628,73 +1823,85 @@
         <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>100</v>
+      </c>
+      <c r="D8" t="s">
+        <v>128</v>
       </c>
       <c r="E8">
-        <v>68053090</v>
+        <v>73262000</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G8">
-        <v>14.17</v>
+        <v>37.93</v>
       </c>
       <c r="J8" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K8" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L8">
-        <v>6.671</v>
+        <v>23.95</v>
       </c>
       <c r="N8" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="P8" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q8" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R8">
-        <v>0.063</v>
+        <v>0.632</v>
       </c>
       <c r="S8">
-        <v>0.063</v>
+        <v>0.632</v>
+      </c>
+      <c r="T8" t="s">
+        <v>141</v>
+      </c>
+      <c r="U8" t="s">
+        <v>141</v>
       </c>
       <c r="V8">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="W8">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="X8">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="AA8" t="s">
-        <v>108</v>
+        <v>160</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>175</v>
       </c>
       <c r="AM8" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="AR8" s="2" t="s">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="AV8" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="AZ8" t="s">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="BF8" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:59">
@@ -1702,73 +1909,85 @@
         <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>101</v>
+      </c>
+      <c r="D9" t="s">
+        <v>128</v>
       </c>
       <c r="E9">
-        <v>68053090</v>
+        <v>73262000</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G9">
-        <v>13.6</v>
+        <v>44.86</v>
       </c>
       <c r="J9" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K9" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L9">
-        <v>6.253</v>
+        <v>28.99</v>
       </c>
       <c r="N9" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="P9" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q9" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R9">
-        <v>0.052</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="S9">
-        <v>0.052</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="T9" t="s">
+        <v>142</v>
+      </c>
+      <c r="U9" t="s">
+        <v>142</v>
       </c>
       <c r="V9">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="W9">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="X9">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="Z9" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="AA9" t="s">
-        <v>108</v>
+        <v>160</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>175</v>
       </c>
       <c r="AM9" t="s">
-        <v>122</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="AR9" s="2" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="AV9" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="AZ9" t="s">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="BF9" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:59">
@@ -1776,144 +1995,159 @@
         <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>102</v>
+      </c>
+      <c r="D10" t="s">
+        <v>129</v>
       </c>
       <c r="E10">
-        <v>96081000</v>
+        <v>73199000</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G10">
-        <v>2.64</v>
+        <v>14.69</v>
       </c>
       <c r="J10" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K10" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L10">
-        <v>0.721</v>
+        <v>7.049</v>
       </c>
       <c r="N10" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="P10" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q10" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R10">
-        <v>0.006</v>
+        <v>0.076</v>
       </c>
       <c r="S10">
-        <v>0.006</v>
+        <v>0.076</v>
       </c>
       <c r="V10">
+        <v>9</v>
+      </c>
+      <c r="W10">
         <v>2</v>
       </c>
-      <c r="W10">
-        <v>15</v>
-      </c>
       <c r="X10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="AA10" t="s">
-        <v>109</v>
+        <v>161</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>176</v>
       </c>
       <c r="AM10" t="s">
-        <v>123</v>
-      </c>
-      <c r="AP10" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="AR10" s="2" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="AV10" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="AZ10" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
       <c r="BF10" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:59">
       <c r="B11" t="s">
         <v>68</v>
       </c>
-      <c r="C11" t="s">
-        <v>87</v>
+      <c r="D11" t="s">
+        <v>129</v>
       </c>
       <c r="E11">
-        <v>39172300</v>
+        <v>73199000</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G11">
-        <v>111.47</v>
+        <v>14.69</v>
       </c>
       <c r="J11" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K11" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L11">
-        <v>77.43300000000001</v>
+        <v>7.049</v>
       </c>
       <c r="N11" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="P11" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q11" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R11">
-        <v>5.4</v>
+        <v>0.076</v>
       </c>
       <c r="S11">
-        <v>5.4</v>
+        <v>0.076</v>
+      </c>
+      <c r="T11" t="s">
+        <v>143</v>
+      </c>
+      <c r="U11" t="s">
+        <v>143</v>
       </c>
       <c r="V11">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="X11">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="Z11" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="AA11" t="s">
-        <v>110</v>
+        <v>161</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>176</v>
       </c>
       <c r="AM11" t="s">
-        <v>124</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AR11" s="2" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="AV11" t="s">
-        <v>171</v>
+        <v>220</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>223</v>
       </c>
       <c r="BF11" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:59">
@@ -1921,70 +2155,76 @@
         <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>103</v>
+      </c>
+      <c r="D12" t="s">
+        <v>128</v>
       </c>
       <c r="E12">
-        <v>39252000</v>
+        <v>68053090</v>
       </c>
       <c r="F12" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G12">
-        <v>148.16</v>
+        <v>14.17</v>
       </c>
       <c r="J12" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K12" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L12">
-        <v>104.12</v>
+        <v>6.671</v>
       </c>
       <c r="N12" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="P12" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q12" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R12">
-        <v>5.22</v>
+        <v>0.063</v>
       </c>
       <c r="S12">
-        <v>5.22</v>
+        <v>0.063</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="W12">
-        <v>212</v>
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="AA12" t="s">
-        <v>111</v>
+        <v>162</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>177</v>
       </c>
       <c r="AM12" t="s">
-        <v>125</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="AR12" s="2" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="AV12" t="s">
-        <v>171</v>
+        <v>220</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>224</v>
       </c>
       <c r="BF12" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:59">
@@ -1992,70 +2232,85 @@
         <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>104</v>
+      </c>
+      <c r="D13" t="s">
+        <v>128</v>
       </c>
       <c r="E13">
-        <v>39252000</v>
+        <v>68053090</v>
       </c>
       <c r="F13" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G13">
-        <v>135.64</v>
+        <v>14.17</v>
       </c>
       <c r="J13" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K13" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L13">
-        <v>95.011</v>
+        <v>6.671</v>
       </c>
       <c r="N13" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="P13" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q13" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R13">
-        <v>4.55</v>
+        <v>0.063</v>
       </c>
       <c r="S13">
-        <v>4.55</v>
+        <v>0.063</v>
+      </c>
+      <c r="T13" t="s">
+        <v>144</v>
+      </c>
+      <c r="U13" t="s">
+        <v>144</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="W13">
-        <v>212</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Z13" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s">
-        <v>111</v>
+        <v>162</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>177</v>
       </c>
       <c r="AM13" t="s">
-        <v>125</v>
-      </c>
-      <c r="AP13" t="s">
-        <v>142</v>
+        <v>191</v>
       </c>
       <c r="AR13" s="2" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="AV13" t="s">
-        <v>171</v>
+        <v>220</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>224</v>
       </c>
       <c r="BF13" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:59">
@@ -2063,70 +2318,85 @@
         <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>105</v>
+      </c>
+      <c r="D14" t="s">
+        <v>128</v>
       </c>
       <c r="E14">
-        <v>39269090</v>
+        <v>68053090</v>
       </c>
       <c r="F14" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G14">
-        <v>18.78</v>
+        <v>13.6</v>
       </c>
       <c r="J14" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K14" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L14">
-        <v>10.021</v>
+        <v>6.253</v>
       </c>
       <c r="N14" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="P14" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q14" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R14">
-        <v>0.32</v>
+        <v>0.052</v>
       </c>
       <c r="S14">
-        <v>0.32</v>
+        <v>0.052</v>
+      </c>
+      <c r="T14" t="s">
+        <v>145</v>
+      </c>
+      <c r="U14" t="s">
+        <v>145</v>
       </c>
       <c r="V14">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X14">
-        <v>35</v>
+        <v>11.5</v>
       </c>
       <c r="Z14" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="AA14" t="s">
-        <v>112</v>
+        <v>162</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>177</v>
       </c>
       <c r="AM14" t="s">
-        <v>126</v>
-      </c>
-      <c r="AP14" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="AR14" s="2" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="AV14" t="s">
-        <v>171</v>
+        <v>220</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>224</v>
       </c>
       <c r="BF14" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:59">
@@ -2134,70 +2404,76 @@
         <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>106</v>
+      </c>
+      <c r="D15" t="s">
+        <v>128</v>
       </c>
       <c r="E15">
-        <v>39173100</v>
+        <v>96081000</v>
       </c>
       <c r="F15" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G15">
-        <v>51.52</v>
+        <v>2.64</v>
       </c>
       <c r="J15" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K15" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L15">
-        <v>33.834</v>
+        <v>0.721</v>
       </c>
       <c r="N15" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="P15" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q15" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R15">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="S15">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="X15">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="AA15" t="s">
-        <v>113</v>
+        <v>163</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>178</v>
       </c>
       <c r="AM15" t="s">
-        <v>127</v>
-      </c>
-      <c r="AP15" t="s">
-        <v>144</v>
+        <v>192</v>
       </c>
       <c r="AR15" s="2" t="s">
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="AV15" t="s">
-        <v>171</v>
+        <v>220</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>225</v>
       </c>
       <c r="BF15" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:59">
@@ -2205,70 +2481,85 @@
         <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>107</v>
+      </c>
+      <c r="D16" t="s">
+        <v>128</v>
       </c>
       <c r="E16">
-        <v>39251000</v>
+        <v>96081000</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G16">
-        <v>355.04</v>
+        <v>2.64</v>
       </c>
       <c r="J16" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K16" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L16">
-        <v>254.571</v>
+        <v>0.721</v>
       </c>
       <c r="N16" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="P16" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q16" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R16">
-        <v>8</v>
+        <v>0.006</v>
       </c>
       <c r="S16">
-        <v>8</v>
+        <v>0.006</v>
+      </c>
+      <c r="T16" t="s">
+        <v>146</v>
+      </c>
+      <c r="U16" t="s">
+        <v>146</v>
       </c>
       <c r="V16">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="W16">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="X16">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="s">
-        <v>114</v>
+        <v>163</v>
       </c>
       <c r="AA16" t="s">
-        <v>114</v>
+        <v>163</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>178</v>
       </c>
       <c r="AM16" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP16" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="AR16" s="2" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="AV16" t="s">
-        <v>171</v>
+        <v>220</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>225</v>
       </c>
       <c r="BF16" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="2:58">
@@ -2276,70 +2567,73 @@
         <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>108</v>
+      </c>
+      <c r="D17" t="s">
+        <v>130</v>
       </c>
       <c r="E17">
-        <v>72162100</v>
+        <v>39172300</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G17">
-        <v>9.289999999999999</v>
+        <v>111.47</v>
       </c>
       <c r="J17" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K17" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L17">
-        <v>3.117</v>
+        <v>77.43300000000001</v>
       </c>
       <c r="N17" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="P17" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q17" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R17">
-        <v>0.12</v>
+        <v>5.4</v>
       </c>
       <c r="S17">
-        <v>0.12</v>
+        <v>5.4</v>
       </c>
       <c r="V17">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="Z17" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="AA17" t="s">
-        <v>115</v>
+        <v>164</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>179</v>
       </c>
       <c r="AM17" t="s">
-        <v>129</v>
-      </c>
-      <c r="AP17" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="AR17" s="2" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="AV17" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="BF17" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="2:58">
@@ -2347,70 +2641,82 @@
         <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>109</v>
+      </c>
+      <c r="D18" t="s">
+        <v>130</v>
       </c>
       <c r="E18">
-        <v>68109900</v>
+        <v>39172300</v>
       </c>
       <c r="F18" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G18">
-        <v>272.15</v>
+        <v>111.47</v>
       </c>
       <c r="J18" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K18" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L18">
-        <v>194.29</v>
+        <v>77.43300000000001</v>
       </c>
       <c r="N18" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="P18" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q18" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R18">
-        <v>13.1</v>
+        <v>5.4</v>
       </c>
       <c r="S18">
-        <v>13.1</v>
+        <v>5.4</v>
+      </c>
+      <c r="T18" t="s">
+        <v>147</v>
+      </c>
+      <c r="U18" t="s">
+        <v>147</v>
       </c>
       <c r="V18">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="W18">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="X18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="Z18" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="AA18" t="s">
-        <v>116</v>
+        <v>164</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>179</v>
       </c>
       <c r="AM18" t="s">
-        <v>130</v>
-      </c>
-      <c r="AP18" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="AR18" s="2" t="s">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="AV18" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="BF18" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="2:58">
@@ -2418,70 +2724,73 @@
         <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>110</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
       </c>
       <c r="E19">
-        <v>39174090</v>
+        <v>39252000</v>
       </c>
       <c r="F19" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G19">
-        <v>6.57</v>
+        <v>148.16</v>
       </c>
       <c r="J19" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K19" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L19">
-        <v>1.792</v>
+        <v>104.12</v>
       </c>
       <c r="N19" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="P19" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q19" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R19">
-        <v>0.021</v>
+        <v>5.22</v>
       </c>
       <c r="S19">
-        <v>0.021</v>
+        <v>5.22</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W19">
+        <v>212</v>
+      </c>
+      <c r="X19">
         <v>10</v>
       </c>
-      <c r="X19">
-        <v>5</v>
-      </c>
       <c r="Z19" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="AA19" t="s">
-        <v>117</v>
+        <v>165</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>180</v>
       </c>
       <c r="AM19" t="s">
-        <v>124</v>
-      </c>
-      <c r="AP19" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="AR19" s="2" t="s">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="AV19" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="BF19" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="2:58">
@@ -2489,70 +2798,82 @@
         <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>111</v>
+      </c>
+      <c r="D20" t="s">
+        <v>130</v>
       </c>
       <c r="E20">
-        <v>39174090</v>
+        <v>39252000</v>
       </c>
       <c r="F20" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G20">
-        <v>3.74</v>
+        <v>148.16</v>
       </c>
       <c r="J20" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="K20" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L20">
-        <v>1.021</v>
+        <v>104.12</v>
       </c>
       <c r="N20" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="P20" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="Q20" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="R20">
-        <v>0.021</v>
+        <v>5.22</v>
       </c>
       <c r="S20">
-        <v>0.021</v>
+        <v>5.22</v>
+      </c>
+      <c r="T20" t="s">
+        <v>148</v>
+      </c>
+      <c r="U20" t="s">
+        <v>148</v>
       </c>
       <c r="V20">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>13</v>
+        <v>212</v>
       </c>
       <c r="X20">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z20" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="AA20" t="s">
-        <v>117</v>
+        <v>165</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>180</v>
       </c>
       <c r="AM20" t="s">
-        <v>124</v>
-      </c>
-      <c r="AP20" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="AR20" s="2" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="AV20" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="BF20" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="2:58">
@@ -2560,70 +2881,1264 @@
         <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>112</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
       </c>
       <c r="E21">
+        <v>39252000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>132</v>
+      </c>
+      <c r="G21">
+        <v>135.64</v>
+      </c>
+      <c r="J21" t="s">
+        <v>133</v>
+      </c>
+      <c r="K21" t="s">
+        <v>132</v>
+      </c>
+      <c r="L21">
+        <v>95.011</v>
+      </c>
+      <c r="N21" t="s">
+        <v>135</v>
+      </c>
+      <c r="P21" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>137</v>
+      </c>
+      <c r="R21">
+        <v>4.55</v>
+      </c>
+      <c r="S21">
+        <v>4.55</v>
+      </c>
+      <c r="T21" t="s">
+        <v>149</v>
+      </c>
+      <c r="U21" t="s">
+        <v>149</v>
+      </c>
+      <c r="V21">
+        <v>8</v>
+      </c>
+      <c r="W21">
+        <v>212</v>
+      </c>
+      <c r="X21">
+        <v>10</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>165</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>180</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>194</v>
+      </c>
+      <c r="AR21" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22" spans="2:58">
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22">
+        <v>39269090</v>
+      </c>
+      <c r="F22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22">
+        <v>18.78</v>
+      </c>
+      <c r="J22" t="s">
+        <v>133</v>
+      </c>
+      <c r="K22" t="s">
+        <v>132</v>
+      </c>
+      <c r="L22">
+        <v>10.021</v>
+      </c>
+      <c r="N22" t="s">
+        <v>135</v>
+      </c>
+      <c r="P22" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>137</v>
+      </c>
+      <c r="R22">
+        <v>0.32</v>
+      </c>
+      <c r="S22">
+        <v>0.32</v>
+      </c>
+      <c r="V22">
+        <v>20</v>
+      </c>
+      <c r="W22">
+        <v>5</v>
+      </c>
+      <c r="X22">
+        <v>35</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>181</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>195</v>
+      </c>
+      <c r="AR22" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF22" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="23" spans="2:58">
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23">
+        <v>39269090</v>
+      </c>
+      <c r="F23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G23">
+        <v>18.78</v>
+      </c>
+      <c r="J23" t="s">
+        <v>133</v>
+      </c>
+      <c r="K23" t="s">
+        <v>132</v>
+      </c>
+      <c r="L23">
+        <v>10.021</v>
+      </c>
+      <c r="N23" t="s">
+        <v>135</v>
+      </c>
+      <c r="P23" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>137</v>
+      </c>
+      <c r="R23">
+        <v>0.32</v>
+      </c>
+      <c r="S23">
+        <v>0.32</v>
+      </c>
+      <c r="T23" t="s">
+        <v>150</v>
+      </c>
+      <c r="U23" t="s">
+        <v>150</v>
+      </c>
+      <c r="V23">
+        <v>20</v>
+      </c>
+      <c r="W23">
+        <v>5</v>
+      </c>
+      <c r="X23">
+        <v>35</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>166</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>181</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>195</v>
+      </c>
+      <c r="AR23" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF23" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="24" spans="2:58">
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24">
+        <v>39173100</v>
+      </c>
+      <c r="F24" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24">
+        <v>51.52</v>
+      </c>
+      <c r="J24" t="s">
+        <v>133</v>
+      </c>
+      <c r="K24" t="s">
+        <v>132</v>
+      </c>
+      <c r="L24">
+        <v>33.834</v>
+      </c>
+      <c r="N24" t="s">
+        <v>135</v>
+      </c>
+      <c r="P24" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>137</v>
+      </c>
+      <c r="R24">
+        <v>0.001</v>
+      </c>
+      <c r="S24">
+        <v>0.001</v>
+      </c>
+      <c r="V24">
+        <v>7</v>
+      </c>
+      <c r="W24">
+        <v>7</v>
+      </c>
+      <c r="X24">
+        <v>50</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>182</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR24" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF24" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="25" spans="2:58">
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25">
+        <v>39173100</v>
+      </c>
+      <c r="F25" t="s">
+        <v>132</v>
+      </c>
+      <c r="G25">
+        <v>51.52</v>
+      </c>
+      <c r="J25" t="s">
+        <v>133</v>
+      </c>
+      <c r="K25" t="s">
+        <v>132</v>
+      </c>
+      <c r="L25">
+        <v>33.834</v>
+      </c>
+      <c r="N25" t="s">
+        <v>135</v>
+      </c>
+      <c r="P25" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>137</v>
+      </c>
+      <c r="R25">
+        <v>0.001</v>
+      </c>
+      <c r="S25">
+        <v>0.001</v>
+      </c>
+      <c r="T25" t="s">
+        <v>151</v>
+      </c>
+      <c r="U25" t="s">
+        <v>151</v>
+      </c>
+      <c r="V25">
+        <v>7</v>
+      </c>
+      <c r="W25">
+        <v>7</v>
+      </c>
+      <c r="X25">
+        <v>50</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>167</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>182</v>
+      </c>
+      <c r="AM25" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR25" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF25" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="26" spans="2:58">
+      <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26">
+        <v>39251000</v>
+      </c>
+      <c r="F26" t="s">
+        <v>132</v>
+      </c>
+      <c r="G26">
+        <v>355.04</v>
+      </c>
+      <c r="J26" t="s">
+        <v>133</v>
+      </c>
+      <c r="K26" t="s">
+        <v>132</v>
+      </c>
+      <c r="L26">
+        <v>254.571</v>
+      </c>
+      <c r="N26" t="s">
+        <v>135</v>
+      </c>
+      <c r="P26" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>137</v>
+      </c>
+      <c r="R26">
+        <v>8</v>
+      </c>
+      <c r="S26">
+        <v>8</v>
+      </c>
+      <c r="V26">
+        <v>70</v>
+      </c>
+      <c r="W26">
+        <v>90</v>
+      </c>
+      <c r="X26">
+        <v>70</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>183</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>197</v>
+      </c>
+      <c r="AR26" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="AV26" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF26" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="2:58">
+      <c r="B27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27">
+        <v>39251000</v>
+      </c>
+      <c r="F27" t="s">
+        <v>132</v>
+      </c>
+      <c r="G27">
+        <v>355.04</v>
+      </c>
+      <c r="J27" t="s">
+        <v>133</v>
+      </c>
+      <c r="K27" t="s">
+        <v>132</v>
+      </c>
+      <c r="L27">
+        <v>254.571</v>
+      </c>
+      <c r="N27" t="s">
+        <v>135</v>
+      </c>
+      <c r="P27" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>137</v>
+      </c>
+      <c r="R27">
+        <v>8</v>
+      </c>
+      <c r="S27">
+        <v>8</v>
+      </c>
+      <c r="T27" t="s">
+        <v>152</v>
+      </c>
+      <c r="U27" t="s">
+        <v>152</v>
+      </c>
+      <c r="V27">
+        <v>70</v>
+      </c>
+      <c r="W27">
+        <v>90</v>
+      </c>
+      <c r="X27">
+        <v>70</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>168</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>183</v>
+      </c>
+      <c r="AM27" t="s">
+        <v>197</v>
+      </c>
+      <c r="AR27" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF27" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="28" spans="2:58">
+      <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28">
+        <v>72162100</v>
+      </c>
+      <c r="F28" t="s">
+        <v>132</v>
+      </c>
+      <c r="G28">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="J28" t="s">
+        <v>133</v>
+      </c>
+      <c r="K28" t="s">
+        <v>132</v>
+      </c>
+      <c r="L28">
+        <v>3.117</v>
+      </c>
+      <c r="N28" t="s">
+        <v>135</v>
+      </c>
+      <c r="P28" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>137</v>
+      </c>
+      <c r="R28">
+        <v>0.12</v>
+      </c>
+      <c r="S28">
+        <v>0.12</v>
+      </c>
+      <c r="V28">
+        <v>22</v>
+      </c>
+      <c r="W28">
+        <v>10</v>
+      </c>
+      <c r="X28">
+        <v>10</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>169</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR28" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="AV28" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF28" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="29" spans="2:58">
+      <c r="B29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29">
+        <v>72162100</v>
+      </c>
+      <c r="F29" t="s">
+        <v>132</v>
+      </c>
+      <c r="G29">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="J29" t="s">
+        <v>133</v>
+      </c>
+      <c r="K29" t="s">
+        <v>132</v>
+      </c>
+      <c r="L29">
+        <v>3.117</v>
+      </c>
+      <c r="N29" t="s">
+        <v>135</v>
+      </c>
+      <c r="P29" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>137</v>
+      </c>
+      <c r="R29">
+        <v>0.12</v>
+      </c>
+      <c r="S29">
+        <v>0.12</v>
+      </c>
+      <c r="T29" t="s">
+        <v>153</v>
+      </c>
+      <c r="U29" t="s">
+        <v>153</v>
+      </c>
+      <c r="V29">
+        <v>22</v>
+      </c>
+      <c r="W29">
+        <v>10</v>
+      </c>
+      <c r="X29">
+        <v>10</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>184</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR29" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="AV29" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF29" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="2:58">
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" t="s">
+        <v>130</v>
+      </c>
+      <c r="E30">
+        <v>68109900</v>
+      </c>
+      <c r="F30" t="s">
+        <v>132</v>
+      </c>
+      <c r="G30">
+        <v>272.15</v>
+      </c>
+      <c r="J30" t="s">
+        <v>133</v>
+      </c>
+      <c r="K30" t="s">
+        <v>132</v>
+      </c>
+      <c r="L30">
+        <v>194.29</v>
+      </c>
+      <c r="N30" t="s">
+        <v>135</v>
+      </c>
+      <c r="P30" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>137</v>
+      </c>
+      <c r="R30">
+        <v>13.1</v>
+      </c>
+      <c r="S30">
+        <v>13.1</v>
+      </c>
+      <c r="V30">
+        <v>60</v>
+      </c>
+      <c r="W30">
+        <v>20</v>
+      </c>
+      <c r="X30">
+        <v>120</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>199</v>
+      </c>
+      <c r="AR30" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="AV30" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF30" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="31" spans="2:58">
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31">
+        <v>68109900</v>
+      </c>
+      <c r="F31" t="s">
+        <v>132</v>
+      </c>
+      <c r="G31">
+        <v>272.15</v>
+      </c>
+      <c r="J31" t="s">
+        <v>133</v>
+      </c>
+      <c r="K31" t="s">
+        <v>132</v>
+      </c>
+      <c r="L31">
+        <v>194.29</v>
+      </c>
+      <c r="N31" t="s">
+        <v>135</v>
+      </c>
+      <c r="P31" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>137</v>
+      </c>
+      <c r="R31">
+        <v>13.1</v>
+      </c>
+      <c r="S31">
+        <v>13.1</v>
+      </c>
+      <c r="T31" t="s">
+        <v>154</v>
+      </c>
+      <c r="U31" t="s">
+        <v>154</v>
+      </c>
+      <c r="V31">
+        <v>60</v>
+      </c>
+      <c r="W31">
+        <v>20</v>
+      </c>
+      <c r="X31">
+        <v>120</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>199</v>
+      </c>
+      <c r="AR31" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="AV31" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF31" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="32" spans="2:58">
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E32">
         <v>39174090</v>
       </c>
-      <c r="F21" t="s">
-        <v>98</v>
-      </c>
-      <c r="G21">
+      <c r="F32" t="s">
+        <v>132</v>
+      </c>
+      <c r="G32">
+        <v>6.57</v>
+      </c>
+      <c r="J32" t="s">
+        <v>133</v>
+      </c>
+      <c r="K32" t="s">
+        <v>132</v>
+      </c>
+      <c r="L32">
+        <v>1.792</v>
+      </c>
+      <c r="N32" t="s">
+        <v>135</v>
+      </c>
+      <c r="P32" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>137</v>
+      </c>
+      <c r="R32">
+        <v>0.021</v>
+      </c>
+      <c r="S32">
+        <v>0.021</v>
+      </c>
+      <c r="V32">
+        <v>5</v>
+      </c>
+      <c r="W32">
+        <v>10</v>
+      </c>
+      <c r="X32">
+        <v>5</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>186</v>
+      </c>
+      <c r="AM32" t="s">
+        <v>193</v>
+      </c>
+      <c r="AR32" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV32" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF32" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33" spans="2:58">
+      <c r="B33" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33">
+        <v>39174090</v>
+      </c>
+      <c r="F33" t="s">
+        <v>132</v>
+      </c>
+      <c r="G33">
+        <v>6.57</v>
+      </c>
+      <c r="J33" t="s">
+        <v>133</v>
+      </c>
+      <c r="K33" t="s">
+        <v>132</v>
+      </c>
+      <c r="L33">
+        <v>1.792</v>
+      </c>
+      <c r="N33" t="s">
+        <v>135</v>
+      </c>
+      <c r="P33" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>137</v>
+      </c>
+      <c r="R33">
+        <v>0.021</v>
+      </c>
+      <c r="S33">
+        <v>0.021</v>
+      </c>
+      <c r="T33" t="s">
+        <v>155</v>
+      </c>
+      <c r="U33" t="s">
+        <v>155</v>
+      </c>
+      <c r="V33">
+        <v>5</v>
+      </c>
+      <c r="W33">
+        <v>10</v>
+      </c>
+      <c r="X33">
+        <v>5</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>171</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>186</v>
+      </c>
+      <c r="AM33" t="s">
+        <v>193</v>
+      </c>
+      <c r="AR33" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="AV33" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF33" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="34" spans="2:58">
+      <c r="B34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34">
+        <v>39174090</v>
+      </c>
+      <c r="F34" t="s">
+        <v>132</v>
+      </c>
+      <c r="G34">
+        <v>3.74</v>
+      </c>
+      <c r="J34" t="s">
+        <v>133</v>
+      </c>
+      <c r="K34" t="s">
+        <v>132</v>
+      </c>
+      <c r="L34">
+        <v>1.021</v>
+      </c>
+      <c r="N34" t="s">
+        <v>135</v>
+      </c>
+      <c r="P34" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>137</v>
+      </c>
+      <c r="R34">
+        <v>0.021</v>
+      </c>
+      <c r="S34">
+        <v>0.021</v>
+      </c>
+      <c r="T34" t="s">
+        <v>156</v>
+      </c>
+      <c r="U34" t="s">
+        <v>156</v>
+      </c>
+      <c r="V34">
+        <v>13</v>
+      </c>
+      <c r="W34">
+        <v>13</v>
+      </c>
+      <c r="X34">
+        <v>12</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>171</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>186</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>193</v>
+      </c>
+      <c r="AR34" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="AV34" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF34" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="35" spans="2:58">
+      <c r="B35" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35">
+        <v>39174090</v>
+      </c>
+      <c r="F35" t="s">
+        <v>132</v>
+      </c>
+      <c r="G35">
         <v>12.62</v>
       </c>
-      <c r="J21" t="s">
-        <v>99</v>
-      </c>
-      <c r="K21" t="s">
-        <v>98</v>
-      </c>
-      <c r="L21">
+      <c r="J35" t="s">
+        <v>133</v>
+      </c>
+      <c r="K35" t="s">
+        <v>132</v>
+      </c>
+      <c r="L35">
         <v>5.544</v>
       </c>
-      <c r="N21" t="s">
-        <v>101</v>
-      </c>
-      <c r="P21" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>103</v>
-      </c>
-      <c r="R21">
+      <c r="N35" t="s">
+        <v>135</v>
+      </c>
+      <c r="P35" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>137</v>
+      </c>
+      <c r="R35">
         <v>0.104</v>
       </c>
-      <c r="S21">
+      <c r="S35">
         <v>0.104</v>
       </c>
-      <c r="V21">
+      <c r="V35">
         <v>14</v>
       </c>
-      <c r="W21">
+      <c r="W35">
         <v>14</v>
       </c>
-      <c r="X21">
+      <c r="X35">
         <v>13</v>
       </c>
-      <c r="Z21" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>118</v>
-      </c>
-      <c r="AM21" t="s">
-        <v>124</v>
-      </c>
-      <c r="AP21" t="s">
-        <v>150</v>
-      </c>
-      <c r="AR21" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AV21" t="s">
-        <v>171</v>
-      </c>
-      <c r="BF21" t="s">
-        <v>177</v>
+      <c r="Z35" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>172</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM35" t="s">
+        <v>193</v>
+      </c>
+      <c r="AR35" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="AV35" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF35" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="36" spans="2:58">
+      <c r="B36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36">
+        <v>39174090</v>
+      </c>
+      <c r="F36" t="s">
+        <v>132</v>
+      </c>
+      <c r="G36">
+        <v>12.62</v>
+      </c>
+      <c r="J36" t="s">
+        <v>133</v>
+      </c>
+      <c r="K36" t="s">
+        <v>132</v>
+      </c>
+      <c r="L36">
+        <v>5.544</v>
+      </c>
+      <c r="N36" t="s">
+        <v>135</v>
+      </c>
+      <c r="P36" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>137</v>
+      </c>
+      <c r="R36">
+        <v>0.104</v>
+      </c>
+      <c r="S36">
+        <v>0.104</v>
+      </c>
+      <c r="T36" t="s">
+        <v>157</v>
+      </c>
+      <c r="U36" t="s">
+        <v>157</v>
+      </c>
+      <c r="V36">
+        <v>14</v>
+      </c>
+      <c r="W36">
+        <v>14</v>
+      </c>
+      <c r="X36">
+        <v>13</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>193</v>
+      </c>
+      <c r="AR36" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="AV36" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF36" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -2648,6 +4163,21 @@
     <hyperlink ref="AR19" r:id="rId18"/>
     <hyperlink ref="AR20" r:id="rId19"/>
     <hyperlink ref="AR21" r:id="rId20"/>
+    <hyperlink ref="AR22" r:id="rId21"/>
+    <hyperlink ref="AR23" r:id="rId22"/>
+    <hyperlink ref="AR24" r:id="rId23"/>
+    <hyperlink ref="AR25" r:id="rId24"/>
+    <hyperlink ref="AR26" r:id="rId25"/>
+    <hyperlink ref="AR27" r:id="rId26"/>
+    <hyperlink ref="AR28" r:id="rId27"/>
+    <hyperlink ref="AR29" r:id="rId28"/>
+    <hyperlink ref="AR30" r:id="rId29"/>
+    <hyperlink ref="AR31" r:id="rId30"/>
+    <hyperlink ref="AR32" r:id="rId31"/>
+    <hyperlink ref="AR33" r:id="rId32"/>
+    <hyperlink ref="AR34" r:id="rId33"/>
+    <hyperlink ref="AR35" r:id="rId34"/>
+    <hyperlink ref="AR36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
